--- a/salidas/Base_resultados_PPDJ_python.xlsx
+++ b/salidas/Base_resultados_PPDJ_python.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH37"/>
+  <dimension ref="A1:AB37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -481,120 +481,90 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Valor_2018</t>
+          <t>Valor_2020</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Meta_2018</t>
+          <t>Meta_2020</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>Diff_2018</t>
+          <t>Diff_2020</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>Valor_2019</t>
+          <t>Valor_2021</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>Meta_2019</t>
+          <t>Meta_2021</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>Diff_2019</t>
+          <t>Diff_2021</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>Valor_2020</t>
+          <t>Valor_2022</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>Meta_2020</t>
+          <t>Meta_2022</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>Diff_2020</t>
+          <t>Diff_2022</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>Valor_2021</t>
+          <t>Valor_2023</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>Meta_2021</t>
+          <t>Meta_2023</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>Diff_2021</t>
+          <t>Diff_2023</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>Valor_2022</t>
+          <t>Valor_2024</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>Meta_2022</t>
+          <t>Meta_2024</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>Diff_2022</t>
+          <t>Diff_2024</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>Valor_2023</t>
+          <t>Valor_2025</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>Meta_2023</t>
+          <t>Meta_2025</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>Diff_2023</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>Valor_2024</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>Meta_2024</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>Diff_2024</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>Valor_2025</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>Meta_2025</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>Diff_2025</t>
         </is>
@@ -631,7 +601,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sector Social</t>
+          <t>Integración Social</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -649,54 +619,52 @@
           <t>2030-12-31</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="M2" t="n">
+        <v>-0.62</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="P2" t="n">
+        <v>-0.63</v>
+      </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>0.63</v>
       </c>
       <c r="R2" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.62</v>
+        <v>-0.01</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>0.78</v>
       </c>
       <c r="U2" t="n">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.63</v>
-      </c>
-      <c r="W2" t="n">
-        <v>0.63</v>
-      </c>
+        <v>0.13</v>
+      </c>
+      <c r="W2" t="inlineStr"/>
       <c r="X2" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>-0.01</v>
-      </c>
+        <v>0.66</v>
+      </c>
+      <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="inlineStr"/>
-      <c r="AD2" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="AE2" t="inlineStr"/>
-      <c r="AF2" t="inlineStr"/>
-      <c r="AG2" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="AH2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -747,54 +715,60 @@
           <t>2030-12-31</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
+      <c r="K3" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.11</v>
+      </c>
       <c r="Q3" t="n">
-        <v>0.44</v>
+        <v>0.34</v>
       </c>
       <c r="R3" t="n">
-        <v>0.32</v>
+        <v>0.34</v>
       </c>
       <c r="S3" t="n">
-        <v>0.12</v>
+        <v>-0</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>0.33</v>
+        <v>0.35</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.33</v>
+        <v>-0.35</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>-0.36</v>
+      </c>
+      <c r="Z3" t="n">
         <v>0.34</v>
       </c>
-      <c r="Y3" t="n">
-        <v>-0.44</v>
-      </c>
-      <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="AB3" t="inlineStr"/>
-      <c r="AC3" t="inlineStr"/>
-      <c r="AD3" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="AE3" t="inlineStr"/>
-      <c r="AF3" t="inlineStr"/>
-      <c r="AG3" t="n">
         <v>0.37</v>
       </c>
-      <c r="AH3" t="inlineStr"/>
+      <c r="AB3" t="n">
+        <v>-0.03</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -845,12 +819,24 @@
           <t>2030-12-31</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M4" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P4" t="n">
+        <v>-0</v>
+      </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
@@ -861,34 +847,32 @@
         <v>-0.1</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
         <v>0.1</v>
       </c>
       <c r="V4" t="n">
-        <v>-0</v>
-      </c>
-      <c r="W4" t="inlineStr"/>
+        <v>-0.1</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
       <c r="X4" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
+        <v>0.11</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0.02</v>
+      </c>
       <c r="AA4" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AB4" t="inlineStr"/>
-      <c r="AC4" t="inlineStr"/>
-      <c r="AD4" t="n">
         <v>0.11</v>
       </c>
-      <c r="AE4" t="inlineStr"/>
-      <c r="AF4" t="inlineStr"/>
-      <c r="AG4" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AH4" t="inlineStr"/>
+      <c r="AB4" t="n">
+        <v>-0.09</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -939,29 +923,41 @@
           <t>2030-12-31</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="O5" t="n">
+        <v>5</v>
+      </c>
+      <c r="P5" t="n">
+        <v>-4.99</v>
+      </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="T5" t="n">
-        <v>0.01</v>
+        <v>2</v>
       </c>
       <c r="U5" t="n">
         <v>5</v>
       </c>
       <c r="V5" t="n">
-        <v>-4.99</v>
+        <v>-3</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
@@ -972,25 +968,11 @@
       <c r="Y5" t="n">
         <v>-5</v>
       </c>
-      <c r="Z5" t="n">
-        <v>2</v>
-      </c>
+      <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="n">
         <v>5</v>
       </c>
-      <c r="AB5" t="n">
-        <v>-3</v>
-      </c>
-      <c r="AC5" t="inlineStr"/>
-      <c r="AD5" t="n">
-        <v>5</v>
-      </c>
-      <c r="AE5" t="inlineStr"/>
-      <c r="AF5" t="inlineStr"/>
-      <c r="AG5" t="n">
-        <v>5</v>
-      </c>
-      <c r="AH5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1041,64 +1023,60 @@
           <t>2030-12-31</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="M6" t="n">
+        <v>-0.92</v>
+      </c>
       <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
+        <v>0.01</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="P6" t="n">
+        <v>-0.91</v>
+      </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="R6" t="n">
         <v>0.92</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.92</v>
+        <v>0.18</v>
       </c>
       <c r="T6" t="n">
-        <v>0.01</v>
+        <v>1.04</v>
       </c>
       <c r="U6" t="n">
         <v>0.92</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.91</v>
+        <v>0.11</v>
       </c>
       <c r="W6" t="n">
-        <v>1.11</v>
+        <v>100.58</v>
       </c>
       <c r="X6" t="n">
         <v>0.92</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.18</v>
+        <v>99.66</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.04</v>
+        <v>102.02</v>
       </c>
       <c r="AA6" t="n">
         <v>0.92</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="AF6" t="inlineStr"/>
-      <c r="AG6" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="AH6" t="inlineStr"/>
+        <v>101.1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1149,31 +1127,41 @@
           <t>2030-12-31</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="M7" t="n">
+        <v>-0.82</v>
+      </c>
       <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
+        <v>0.01</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="P7" t="n">
+        <v>-0.82</v>
+      </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>0.98</v>
       </c>
       <c r="R7" t="n">
         <v>0.82</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.82</v>
+        <v>0.16</v>
       </c>
       <c r="T7" t="n">
-        <v>0.01</v>
+        <v>0.99</v>
       </c>
       <c r="U7" t="n">
         <v>0.82</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.82</v>
+        <v>0.16</v>
       </c>
       <c r="W7" t="n">
         <v>0.98</v>
@@ -1182,31 +1170,17 @@
         <v>0.82</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.99</v>
+        <v>101.79</v>
       </c>
       <c r="AA7" t="n">
         <v>0.82</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="AF7" t="inlineStr"/>
-      <c r="AG7" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="AH7" t="inlineStr"/>
+        <v>100.97</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1257,60 +1231,60 @@
           <t>2030-12-31</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="M8" t="n">
+        <v>-0.5600000000000001</v>
+      </c>
       <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
+        <v>0.48</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="P8" t="n">
+        <v>-0.08</v>
+      </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>0.48</v>
       </c>
       <c r="R8" t="n">
         <v>0.5600000000000001</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.08</v>
       </c>
       <c r="T8" t="n">
-        <v>0.48</v>
+        <v>0.52</v>
       </c>
       <c r="U8" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.57</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.08</v>
+        <v>-0.05</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.57</v>
       </c>
       <c r="Y8" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.57</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.03</v>
+        <v>0.54</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.57</v>
+        <v>0.58</v>
       </c>
       <c r="AB8" t="n">
-        <v>-0.54</v>
-      </c>
-      <c r="AC8" t="inlineStr"/>
-      <c r="AD8" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="AE8" t="inlineStr"/>
-      <c r="AF8" t="inlineStr"/>
-      <c r="AG8" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="AH8" t="inlineStr"/>
+        <v>-0.04</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1361,22 +1335,32 @@
           <t>2030-12-31</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" t="n">
+        <v>-1</v>
+      </c>
       <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R9" t="n">
         <v>1</v>
       </c>
       <c r="S9" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
         <v>1</v>
@@ -1394,7 +1378,7 @@
         <v>1</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z9" t="n">
         <v>1</v>
@@ -1405,20 +1389,6 @@
       <c r="AB9" t="n">
         <v>0</v>
       </c>
-      <c r="AC9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>-0</v>
-      </c>
-      <c r="AF9" t="inlineStr"/>
-      <c r="AG9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1469,22 +1439,32 @@
           <t>2030-12-31</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="M10" t="n">
+        <v>-0.32</v>
+      </c>
       <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
+        <v>0.35</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0.03</v>
+      </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="R10" t="n">
         <v>0.32</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.32</v>
+        <v>0.03</v>
       </c>
       <c r="T10" t="n">
         <v>0.35</v>
@@ -1496,37 +1476,23 @@
         <v>0.03</v>
       </c>
       <c r="W10" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="X10" t="n">
         <v>0.32</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="AA10" t="n">
         <v>0.32</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="AE10" t="n">
         <v>0.01</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
-      <c r="AG10" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="AH10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1577,64 +1543,60 @@
           <t>2030-12-31</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="M11" t="n">
+        <v>-1.53</v>
+      </c>
       <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
+        <v>1.4</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="P11" t="n">
+        <v>-0.13</v>
+      </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="R11" t="n">
         <v>1.53</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.53</v>
+        <v>-1.52</v>
       </c>
       <c r="T11" t="n">
-        <v>1.4</v>
+        <v>0.04</v>
       </c>
       <c r="U11" t="n">
         <v>1.53</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.13</v>
+        <v>-1.5</v>
       </c>
       <c r="W11" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="X11" t="n">
         <v>1.53</v>
       </c>
       <c r="Y11" t="n">
-        <v>-1.52</v>
+        <v>-1.51</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.04</v>
+        <v>2</v>
       </c>
       <c r="AA11" t="n">
         <v>1.53</v>
       </c>
       <c r="AB11" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>-1.51</v>
-      </c>
-      <c r="AF11" t="inlineStr"/>
-      <c r="AG11" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AH11" t="inlineStr"/>
+        <v>0.47</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1648,16 +1610,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2.7. Jóvenes que cuentan con las condiciones para permanecer en la educación Universitaria .</t>
+          <t>2.8. Jóvenes que cuentan con las condiciones para permanecer en la educación superior.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Deserción por cohorte universitaria</t>
+          <t>Deserción anual en programas de educación superior.</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1677,7 +1639,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2019-01-01</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1685,7 +1647,9 @@
           <t>2030-12-31</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="n">
@@ -1696,49 +1660,27 @@
       <c r="Q12" t="n">
         <v>0</v>
       </c>
-      <c r="R12" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="S12" t="n">
-        <v>-0.45</v>
-      </c>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
       <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="n">
         <v>0.09</v>
       </c>
-      <c r="U12" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="V12" t="n">
-        <v>-0.36</v>
-      </c>
-      <c r="W12" t="n">
+      <c r="AA12" t="n">
         <v>0.09</v>
       </c>
-      <c r="X12" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>-0.36</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>0.45</v>
-      </c>
       <c r="AB12" t="n">
-        <v>-0.35</v>
-      </c>
-      <c r="AC12" t="inlineStr"/>
-      <c r="AD12" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="AE12" t="inlineStr"/>
-      <c r="AF12" t="inlineStr"/>
-      <c r="AG12" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="AH12" t="inlineStr"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1752,7 +1694,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1789,62 +1731,60 @@
           <t>2030-12-31</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
+      <c r="K13" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="P13" t="n">
+        <v>-0.02</v>
+      </c>
       <c r="Q13" t="n">
-        <v>0.62</v>
+        <v>0.91</v>
       </c>
       <c r="R13" t="n">
-        <v>0.25</v>
+        <v>0.28</v>
       </c>
       <c r="S13" t="n">
-        <v>0.37</v>
+        <v>0.63</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.37</v>
+        <v>0.31</v>
       </c>
       <c r="U13" t="n">
-        <v>0.27</v>
+        <v>0.3</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.64</v>
+        <v>0.01</v>
       </c>
       <c r="W13" t="n">
-        <v>0.66</v>
+        <v>0.5</v>
       </c>
       <c r="X13" t="n">
-        <v>0.28</v>
+        <v>0.31</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.38</v>
+        <v>0.19</v>
       </c>
       <c r="Z13" t="n">
-        <v>-0.6</v>
+        <v>1.17</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.3</v>
+        <v>0.33</v>
       </c>
       <c r="AB13" t="n">
-        <v>-0.9</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>-0.12</v>
-      </c>
-      <c r="AF13" t="inlineStr"/>
-      <c r="AG13" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AH13" t="inlineStr"/>
+        <v>0.84</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1858,7 +1798,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1895,62 +1835,60 @@
           <t>2030-12-31</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="M14" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="P14" t="n">
+        <v>-0.4</v>
+      </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>0.13</v>
       </c>
       <c r="R14" t="n">
         <v>0.4</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.4</v>
+        <v>-0.27</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="U14" t="n">
         <v>0.4</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.4</v>
+        <v>-0.29</v>
       </c>
       <c r="W14" t="n">
-        <v>0.13</v>
+        <v>0.17</v>
       </c>
       <c r="X14" t="n">
         <v>0.4</v>
       </c>
       <c r="Y14" t="n">
-        <v>-0.27</v>
+        <v>-0.23</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.11</v>
+        <v>0.16</v>
       </c>
       <c r="AA14" t="n">
         <v>0.4</v>
       </c>
       <c r="AB14" t="n">
-        <v>-0.29</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>-0.23</v>
-      </c>
-      <c r="AF14" t="inlineStr"/>
-      <c r="AG14" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AH14" t="inlineStr"/>
+        <v>-0.24</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1964,7 +1902,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2001,62 +1939,60 @@
           <t>2030-12-31</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
+      <c r="K15" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="N15" t="n">
+        <v>4.94</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="P15" t="n">
+        <v>4.69</v>
+      </c>
       <c r="Q15" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="U15" t="n">
         <v>0.28</v>
       </c>
-      <c r="R15" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="S15" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="T15" t="n">
-        <v>4.66</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0.25</v>
-      </c>
       <c r="V15" t="n">
-        <v>4.41</v>
+        <v>0.09</v>
       </c>
       <c r="W15" t="n">
-        <v>-4.58</v>
+        <v>0.36</v>
       </c>
       <c r="X15" t="n">
-        <v>0.27</v>
+        <v>0.29</v>
       </c>
       <c r="Y15" t="n">
-        <v>-4.84</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>0.36</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.28</v>
+        <v>0.3</v>
       </c>
       <c r="AB15" t="n">
-        <v>-0.28</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>-0.29</v>
-      </c>
-      <c r="AF15" t="inlineStr"/>
-      <c r="AG15" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="AH15" t="inlineStr"/>
+        <v>0.06</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2070,7 +2006,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2107,62 +2043,60 @@
           <t>2030-12-31</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
+      <c r="K16" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="L16" t="n">
+        <v>6.86</v>
+      </c>
+      <c r="M16" t="n">
+        <v>-1.76</v>
+      </c>
+      <c r="N16" t="n">
+        <v>4.94</v>
+      </c>
+      <c r="O16" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="P16" t="n">
+        <v>-2.76</v>
+      </c>
       <c r="Q16" t="n">
-        <v>5.1</v>
+        <v>9.33</v>
       </c>
       <c r="R16" t="n">
-        <v>6.86</v>
+        <v>7.7</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.76</v>
+        <v>1.63</v>
       </c>
       <c r="T16" t="n">
-        <v>4.94</v>
+        <v>8.66</v>
       </c>
       <c r="U16" t="n">
         <v>7.7</v>
       </c>
       <c r="V16" t="n">
-        <v>-2.76</v>
+        <v>0.96</v>
       </c>
       <c r="W16" t="n">
-        <v>9.33</v>
+        <v>7.5</v>
       </c>
       <c r="X16" t="n">
         <v>7.7</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.63</v>
+        <v>-0.2</v>
       </c>
       <c r="Z16" t="n">
-        <v>8.66</v>
+        <v>6.3</v>
       </c>
       <c r="AA16" t="n">
         <v>7.7</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="AF16" t="inlineStr"/>
-      <c r="AG16" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="AH16" t="inlineStr"/>
+        <v>-1.4</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2176,7 +2110,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2185,12 +2119,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Proporción de prevalencia de personas entre 14 a 28 años residentes en Bogotá que tuvieron consumo adictivo o problemático de SPA e ingresaron a tratamiento.</t>
+          <t>Edad promedio de inicio de consumo abusivo de sustancias psicoactivas en población de 14 a 28 años en el Distrito Capital.</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Porcentaje</t>
+          <t>Valor</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2213,62 +2147,60 @@
           <t>2030-12-31</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
+      <c r="K17" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="L17" t="n">
+        <v>81.77</v>
+      </c>
+      <c r="M17" t="n">
+        <v>-66.87</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="P17" t="n">
+        <v>-14.7</v>
+      </c>
       <c r="Q17" t="n">
-        <v>14.9</v>
+        <v>14.1</v>
       </c>
       <c r="R17" t="n">
-        <v>81.77</v>
+        <v>14.7</v>
       </c>
       <c r="S17" t="n">
-        <v>-66.87</v>
+        <v>-0.6</v>
       </c>
       <c r="T17" t="n">
-        <v>14.4</v>
+        <v>14.22</v>
       </c>
       <c r="U17" t="n">
         <v>14.7</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.3</v>
+        <v>-0.48</v>
       </c>
       <c r="W17" t="n">
-        <v>14.1</v>
+        <v>15.01</v>
       </c>
       <c r="X17" t="n">
         <v>14.7</v>
       </c>
       <c r="Y17" t="n">
-        <v>-0.6</v>
+        <v>0.31</v>
       </c>
       <c r="Z17" t="n">
-        <v>14.22</v>
+        <v>13.75</v>
       </c>
       <c r="AA17" t="n">
         <v>14.7</v>
       </c>
       <c r="AB17" t="n">
-        <v>-0.48</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>15.01</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>14.7</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="AF17" t="inlineStr"/>
-      <c r="AG17" t="n">
-        <v>14.7</v>
-      </c>
-      <c r="AH17" t="inlineStr"/>
+        <v>-0.95</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2282,7 +2214,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2319,62 +2251,60 @@
           <t>2030-12-31</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
+      <c r="K18" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="M18" t="n">
+        <v>27.16</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="O18" t="n">
+        <v>34.6</v>
+      </c>
+      <c r="P18" t="n">
+        <v>-34.3</v>
+      </c>
       <c r="Q18" t="n">
-        <v>27.5</v>
+        <v>0.22</v>
       </c>
       <c r="R18" t="n">
-        <v>0.34</v>
+        <v>32.8</v>
       </c>
       <c r="S18" t="n">
-        <v>27.16</v>
+        <v>-32.58</v>
       </c>
       <c r="T18" t="n">
-        <v>0.3</v>
+        <v>41.4</v>
       </c>
       <c r="U18" t="n">
-        <v>34.6</v>
+        <v>31.1</v>
       </c>
       <c r="V18" t="n">
-        <v>-34.3</v>
+        <v>10.3</v>
       </c>
       <c r="W18" t="n">
-        <v>0.22</v>
+        <v>16.83</v>
       </c>
       <c r="X18" t="n">
-        <v>32.8</v>
+        <v>29.5</v>
       </c>
       <c r="Y18" t="n">
-        <v>-32.58</v>
+        <v>-12.67</v>
       </c>
       <c r="Z18" t="n">
-        <v>41.4</v>
+        <v>16.3</v>
       </c>
       <c r="AA18" t="n">
-        <v>31.1</v>
+        <v>29.5</v>
       </c>
       <c r="AB18" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>16.83</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>29.5</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>-12.67</v>
-      </c>
-      <c r="AF18" t="inlineStr"/>
-      <c r="AG18" t="n">
-        <v>29.5</v>
-      </c>
-      <c r="AH18" t="inlineStr"/>
+        <v>-13.2</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2388,7 +2318,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2425,62 +2355,60 @@
           <t>2030-12-31</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
+      <c r="K19" t="n">
+        <v>84.2</v>
+      </c>
+      <c r="L19" t="n">
+        <v>86.09999999999999</v>
+      </c>
+      <c r="M19" t="n">
+        <v>-1.9</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>86.5</v>
+      </c>
+      <c r="P19" t="n">
+        <v>-86.5</v>
+      </c>
       <c r="Q19" t="n">
-        <v>84.2</v>
+        <v>102.8</v>
       </c>
       <c r="R19" t="n">
-        <v>86.09999999999999</v>
+        <v>87</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.9</v>
+        <v>15.8</v>
       </c>
       <c r="T19" t="n">
-        <v>17.6</v>
+        <v>99.3</v>
       </c>
       <c r="U19" t="n">
-        <v>86.5</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="V19" t="n">
-        <v>-68.90000000000001</v>
+        <v>11.9</v>
       </c>
       <c r="W19" t="n">
-        <v>1</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="X19" t="n">
-        <v>87</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="Y19" t="n">
-        <v>-86</v>
+        <v>11.7</v>
       </c>
       <c r="Z19" t="n">
-        <v>-3.5</v>
+        <v>88.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>87.40000000000001</v>
+        <v>87.8</v>
       </c>
       <c r="AB19" t="n">
-        <v>-90.90000000000001</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>87.40000000000001</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>-87.59999999999999</v>
-      </c>
-      <c r="AF19" t="inlineStr"/>
-      <c r="AG19" t="n">
-        <v>87.8</v>
-      </c>
-      <c r="AH19" t="inlineStr"/>
+        <v>0.7</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2494,7 +2422,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2531,62 +2459,60 @@
           <t>2030-12-31</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr"/>
+      <c r="K20" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L20" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="M20" t="n">
+        <v>-9.199999999999999</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0.1</v>
+      </c>
       <c r="Q20" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>9.4</v>
+        <v>0.11</v>
       </c>
       <c r="S20" t="n">
-        <v>-9.199999999999999</v>
+        <v>-0.11</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.1</v>
+        <v>-0.09</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="X20" t="n">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="Y20" t="n">
-        <v>-0.11</v>
+        <v>-0.06</v>
       </c>
       <c r="Z20" t="n">
-        <v>0.03</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AA20" t="n">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="AB20" t="n">
-        <v>-0.09</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>-0.09</v>
-      </c>
-      <c r="AF20" t="inlineStr"/>
-      <c r="AG20" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="AH20" t="inlineStr"/>
+        <v>-0.07000000000000001</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2600,7 +2526,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2637,62 +2563,60 @@
           <t>2030-12-31</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr"/>
+      <c r="K21" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="M21" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="P21" t="n">
+        <v>-0.16</v>
+      </c>
       <c r="Q21" t="n">
-        <v>0.18</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.32</v>
+        <v>0.36</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.14</v>
+        <v>-0.36</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="U21" t="n">
-        <v>0.34</v>
+        <v>0.38</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.34</v>
+        <v>-0.24</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="X21" t="n">
-        <v>0.36</v>
+        <v>0.38</v>
       </c>
       <c r="Y21" t="n">
-        <v>-0.36</v>
+        <v>-0.25</v>
       </c>
       <c r="Z21" t="n">
         <v>0.14</v>
       </c>
       <c r="AA21" t="n">
-        <v>0.38</v>
+        <v>0.4</v>
       </c>
       <c r="AB21" t="n">
-        <v>-0.24</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>-0.39</v>
-      </c>
-      <c r="AF21" t="inlineStr"/>
-      <c r="AG21" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AH21" t="inlineStr"/>
+        <v>-0.27</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2706,7 +2630,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2743,62 +2667,60 @@
           <t>2030-12-31</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr"/>
+      <c r="K22" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="L22" t="n">
+        <v>5</v>
+      </c>
+      <c r="M22" t="n">
+        <v>-3.8</v>
+      </c>
+      <c r="N22" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="O22" t="n">
+        <v>5</v>
+      </c>
+      <c r="P22" t="n">
+        <v>-3.8</v>
+      </c>
       <c r="Q22" t="n">
-        <v>1.2</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="R22" t="n">
         <v>5</v>
       </c>
       <c r="S22" t="n">
-        <v>-3.8</v>
+        <v>-4.93</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>6.03</v>
       </c>
       <c r="U22" t="n">
         <v>5</v>
       </c>
       <c r="V22" t="n">
-        <v>-5</v>
+        <v>1.03</v>
       </c>
       <c r="W22" t="n">
-        <v>-1.13</v>
+        <v>4.4</v>
       </c>
       <c r="X22" t="n">
         <v>5</v>
       </c>
       <c r="Y22" t="n">
-        <v>-6.13</v>
+        <v>-0.6</v>
       </c>
       <c r="Z22" t="n">
-        <v>5.96</v>
+        <v>4.4</v>
       </c>
       <c r="AA22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>-1.63</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>5</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>-6.63</v>
-      </c>
-      <c r="AF22" t="inlineStr"/>
-      <c r="AG22" t="n">
-        <v>6</v>
-      </c>
-      <c r="AH22" t="inlineStr"/>
+        <v>-1.6</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2812,7 +2734,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2849,62 +2771,60 @@
           <t>2030-12-31</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr"/>
+      <c r="K23" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="M23" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="P23" t="n">
+        <v>-0.22</v>
+      </c>
       <c r="Q23" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="R23" t="n">
-        <v>0.48</v>
+        <v>0.58</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.15</v>
+        <v>-0.08</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="U23" t="n">
-        <v>0.55</v>
+        <v>0.61</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.55</v>
+        <v>-0.11</v>
       </c>
       <c r="W23" t="n">
-        <v>0.17</v>
+        <v>0.52</v>
       </c>
       <c r="X23" t="n">
-        <v>0.58</v>
+        <v>0.61</v>
       </c>
       <c r="Y23" t="n">
-        <v>-0.41</v>
+        <v>-0.09</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>0.52</v>
       </c>
       <c r="AA23" t="n">
-        <v>0.61</v>
+        <v>0.64</v>
       </c>
       <c r="AB23" t="n">
-        <v>-0.61</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>-0.59</v>
-      </c>
-      <c r="AF23" t="inlineStr"/>
-      <c r="AG23" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="AH23" t="inlineStr"/>
+        <v>-0.12</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2918,7 +2838,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2955,58 +2875,60 @@
           <t>2030-12-31</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr"/>
+      <c r="K24" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="M24" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="P24" t="n">
+        <v>-0.14</v>
+      </c>
       <c r="Q24" t="n">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="R24" t="n">
-        <v>0.52</v>
+        <v>0.55</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.12</v>
+        <v>-0.14</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>0.41</v>
       </c>
       <c r="U24" t="n">
-        <v>0.54</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.54</v>
+        <v>-0.15</v>
       </c>
       <c r="W24" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="Y24" t="n">
-        <v>-0.54</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>0.41</v>
       </c>
       <c r="AA24" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.57</v>
       </c>
       <c r="AB24" t="n">
-        <v>-0.5600000000000001</v>
-      </c>
-      <c r="AC24" t="inlineStr"/>
-      <c r="AD24" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="AE24" t="inlineStr"/>
-      <c r="AF24" t="inlineStr"/>
-      <c r="AG24" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="AH24" t="inlineStr"/>
+        <v>-0.16</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3020,7 +2942,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3057,54 +2979,56 @@
           <t>2030-12-31</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
-      <c r="P25" t="inlineStr"/>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>473.5</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-473.5</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>459.5</v>
+      </c>
+      <c r="P25" t="n">
+        <v>-459.5</v>
+      </c>
       <c r="Q25" t="n">
         <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>473.5</v>
+        <v>452.5</v>
       </c>
       <c r="S25" t="n">
-        <v>-473.5</v>
+        <v>-452.5</v>
       </c>
       <c r="T25" t="n">
         <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>459.5</v>
+        <v>445.5</v>
       </c>
       <c r="V25" t="n">
-        <v>-459.5</v>
-      </c>
-      <c r="W25" t="inlineStr"/>
+        <v>-445.5</v>
+      </c>
+      <c r="W25" t="n">
+        <v>333</v>
+      </c>
       <c r="X25" t="n">
-        <v>452.5</v>
-      </c>
-      <c r="Y25" t="inlineStr"/>
+        <v>445.5</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>-112.5</v>
+      </c>
       <c r="Z25" t="inlineStr"/>
       <c r="AA25" t="n">
-        <v>445.5</v>
+        <v>438.5</v>
       </c>
       <c r="AB25" t="inlineStr"/>
-      <c r="AC25" t="n">
-        <v>333</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>445.5</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>-112.5</v>
-      </c>
-      <c r="AF25" t="inlineStr"/>
-      <c r="AG25" t="n">
-        <v>438.5</v>
-      </c>
-      <c r="AH25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3118,7 +3042,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3155,62 +3079,56 @@
           <t>2030-12-31</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
-      <c r="P26" t="inlineStr"/>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1079</v>
+      </c>
+      <c r="M26" t="n">
+        <v>-1079</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>1062.26</v>
+      </c>
+      <c r="P26" t="n">
+        <v>-1062.26</v>
+      </c>
       <c r="Q26" t="n">
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>1079</v>
+        <v>1045.83</v>
       </c>
       <c r="S26" t="n">
-        <v>-1079</v>
+        <v>-1045.83</v>
       </c>
       <c r="T26" t="n">
         <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>1062.26</v>
+        <v>1029.4</v>
       </c>
       <c r="V26" t="n">
-        <v>-1062.26</v>
+        <v>-1029.4</v>
       </c>
       <c r="W26" t="n">
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>1045.83</v>
+        <v>1029</v>
       </c>
       <c r="Y26" t="n">
-        <v>-1045.83</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>0</v>
-      </c>
+        <v>-1029</v>
+      </c>
+      <c r="Z26" t="inlineStr"/>
       <c r="AA26" t="n">
-        <v>1029.4</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>-1029.4</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>1029</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>-1029</v>
-      </c>
-      <c r="AF26" t="inlineStr"/>
-      <c r="AG26" t="n">
         <v>1013</v>
       </c>
-      <c r="AH26" t="inlineStr"/>
+      <c r="AB26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3224,7 +3142,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3261,54 +3179,60 @@
           <t>2030-12-31</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr"/>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>242</v>
+      </c>
+      <c r="M27" t="n">
+        <v>-242</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>235</v>
+      </c>
+      <c r="P27" t="n">
+        <v>-235</v>
+      </c>
       <c r="Q27" t="n">
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>242</v>
+        <v>229</v>
       </c>
       <c r="S27" t="n">
-        <v>-242</v>
+        <v>-229</v>
       </c>
       <c r="T27" t="n">
-        <v>1090</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>235</v>
+        <v>223</v>
       </c>
       <c r="V27" t="n">
-        <v>855</v>
-      </c>
-      <c r="W27" t="inlineStr"/>
+        <v>-223</v>
+      </c>
+      <c r="W27" t="n">
+        <v>84</v>
+      </c>
       <c r="X27" t="n">
-        <v>229</v>
-      </c>
-      <c r="Y27" t="inlineStr"/>
-      <c r="Z27" t="inlineStr"/>
+        <v>223</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>-139</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>331</v>
+      </c>
       <c r="AA27" t="n">
-        <v>223</v>
-      </c>
-      <c r="AB27" t="inlineStr"/>
-      <c r="AC27" t="n">
-        <v>84</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>223</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>-139</v>
-      </c>
-      <c r="AF27" t="inlineStr"/>
-      <c r="AG27" t="n">
         <v>218</v>
       </c>
-      <c r="AH27" t="inlineStr"/>
+      <c r="AB27" t="n">
+        <v>113</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3322,7 +3246,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3359,58 +3283,60 @@
           <t>2030-12-31</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr"/>
+      <c r="K28" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L28" t="n">
+        <v>1</v>
+      </c>
+      <c r="M28" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="O28" t="n">
+        <v>1</v>
+      </c>
+      <c r="P28" t="n">
+        <v>-0.49</v>
+      </c>
       <c r="Q28" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="R28" t="n">
         <v>1</v>
       </c>
       <c r="S28" t="n">
-        <v>-0.6</v>
+        <v>0.1</v>
       </c>
       <c r="T28" t="n">
-        <v>0.51</v>
+        <v>1.62</v>
       </c>
       <c r="U28" t="n">
         <v>1</v>
       </c>
       <c r="V28" t="n">
-        <v>-0.49</v>
+        <v>0.62</v>
       </c>
       <c r="W28" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
         <v>1</v>
       </c>
       <c r="Y28" t="n">
-        <v>0.1</v>
+        <v>-1</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.62</v>
+        <v>3.06</v>
       </c>
       <c r="AA28" t="n">
         <v>1</v>
       </c>
       <c r="AB28" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="AC28" t="inlineStr"/>
-      <c r="AD28" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE28" t="inlineStr"/>
-      <c r="AF28" t="inlineStr"/>
-      <c r="AG28" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH28" t="inlineStr"/>
+        <v>2.06</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3424,7 +3350,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3461,58 +3387,60 @@
           <t>2030-12-31</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
-      <c r="P29" t="inlineStr"/>
+      <c r="K29" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0.8100000000000001</v>
+      </c>
       <c r="Q29" t="n">
-        <v>0.4</v>
+        <v>3.04</v>
       </c>
       <c r="R29" t="n">
         <v>0.01</v>
       </c>
       <c r="S29" t="n">
-        <v>0.39</v>
+        <v>3.03</v>
       </c>
       <c r="T29" t="n">
-        <v>0.82</v>
+        <v>3.83</v>
       </c>
       <c r="U29" t="n">
         <v>0.01</v>
       </c>
       <c r="V29" t="n">
-        <v>0.8100000000000001</v>
+        <v>3.82</v>
       </c>
       <c r="W29" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
         <v>0.01</v>
       </c>
       <c r="Y29" t="n">
-        <v>3.03</v>
+        <v>-0.01</v>
       </c>
       <c r="Z29" t="n">
-        <v>3.83</v>
+        <v>4.66</v>
       </c>
       <c r="AA29" t="n">
         <v>0.01</v>
       </c>
       <c r="AB29" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="AC29" t="inlineStr"/>
-      <c r="AD29" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="AE29" t="inlineStr"/>
-      <c r="AF29" t="inlineStr"/>
-      <c r="AG29" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="AH29" t="inlineStr"/>
+        <v>4.65</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3526,7 +3454,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3563,62 +3491,56 @@
           <t>2030-12-31</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr"/>
-      <c r="P30" t="inlineStr"/>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="M30" t="n">
+        <v>-0.89</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="P30" t="n">
+        <v>-0.88</v>
+      </c>
       <c r="Q30" t="n">
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>0.89</v>
+        <v>0.87</v>
       </c>
       <c r="S30" t="n">
-        <v>-0.89</v>
+        <v>-0.87</v>
       </c>
       <c r="T30" t="n">
         <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>0.88</v>
+        <v>0.86</v>
       </c>
       <c r="V30" t="n">
-        <v>-0.88</v>
+        <v>-0.86</v>
       </c>
       <c r="W30" t="n">
         <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>0.87</v>
+        <v>0.86</v>
       </c>
       <c r="Y30" t="n">
-        <v>-0.87</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>0</v>
-      </c>
+        <v>-0.86</v>
+      </c>
+      <c r="Z30" t="inlineStr"/>
       <c r="AA30" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>-0.86</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>-0.86</v>
-      </c>
-      <c r="AF30" t="inlineStr"/>
-      <c r="AG30" t="n">
         <v>0.85</v>
       </c>
-      <c r="AH30" t="inlineStr"/>
+      <c r="AB30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3632,7 +3554,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3669,12 +3591,24 @@
           <t>2030-12-31</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr"/>
-      <c r="P31" t="inlineStr"/>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="M31" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="P31" t="n">
+        <v>-0.7</v>
+      </c>
       <c r="Q31" t="n">
         <v>0</v>
       </c>
@@ -3685,46 +3619,32 @@
         <v>-0.7</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="U31" t="n">
         <v>0.7</v>
       </c>
       <c r="V31" t="n">
-        <v>-0.7</v>
+        <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X31" t="n">
         <v>0.7</v>
       </c>
       <c r="Y31" t="n">
-        <v>-0.7</v>
+        <v>0.3</v>
       </c>
       <c r="Z31" t="n">
-        <v>0.7</v>
+        <v>0.98</v>
       </c>
       <c r="AA31" t="n">
         <v>0.7</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="AF31" t="inlineStr"/>
-      <c r="AG31" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="AH31" t="inlineStr"/>
+        <v>0.28</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -3738,7 +3658,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3775,12 +3695,24 @@
           <t>2030-12-31</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr"/>
-      <c r="P32" t="inlineStr"/>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="M32" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="P32" t="n">
+        <v>-0.19</v>
+      </c>
       <c r="Q32" t="n">
         <v>0</v>
       </c>
@@ -3808,29 +3740,11 @@
       <c r="Y32" t="n">
         <v>-0.19</v>
       </c>
-      <c r="Z32" t="n">
-        <v>0</v>
-      </c>
+      <c r="Z32" t="inlineStr"/>
       <c r="AA32" t="n">
         <v>0.19</v>
       </c>
-      <c r="AB32" t="n">
-        <v>-0.19</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>-0.19</v>
-      </c>
-      <c r="AF32" t="inlineStr"/>
-      <c r="AG32" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="AH32" t="inlineStr"/>
+      <c r="AB32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -3844,7 +3758,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3881,62 +3795,60 @@
           <t>2030-12-31</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr"/>
-      <c r="P33" t="inlineStr"/>
+      <c r="K33" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="M33" t="n">
+        <v>-0.51</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="P33" t="n">
+        <v>-0.61</v>
+      </c>
       <c r="Q33" t="n">
-        <v>10.05</v>
+        <v>0.25</v>
       </c>
       <c r="R33" t="n">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="S33" t="n">
-        <v>9.44</v>
+        <v>-0.36</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>0.98</v>
       </c>
       <c r="U33" t="n">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="V33" t="n">
-        <v>-0.61</v>
+        <v>0.36</v>
       </c>
       <c r="W33" t="n">
-        <v>25256</v>
+        <v>0.99</v>
       </c>
       <c r="X33" t="n">
         <v>0.62</v>
       </c>
       <c r="Y33" t="n">
-        <v>25255.38</v>
+        <v>0.37</v>
       </c>
       <c r="Z33" t="n">
-        <v>-25255.02</v>
+        <v>0.99</v>
       </c>
       <c r="AA33" t="n">
         <v>0.62</v>
       </c>
       <c r="AB33" t="n">
-        <v>-25255.64</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>-0.61</v>
-      </c>
-      <c r="AF33" t="inlineStr"/>
-      <c r="AG33" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="AH33" t="inlineStr"/>
+        <v>0.37</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -3950,7 +3862,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3987,58 +3899,52 @@
           <t>2030-12-31</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr"/>
-      <c r="P34" t="inlineStr"/>
+      <c r="K34" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="M34" t="n">
+        <v>-0.21</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="P34" t="n">
+        <v>-0.06</v>
+      </c>
       <c r="Q34" t="n">
-        <v>0.24</v>
+        <v>1</v>
       </c>
       <c r="R34" t="n">
-        <v>0.45</v>
+        <v>0.48</v>
       </c>
       <c r="S34" t="n">
-        <v>-0.21</v>
+        <v>0.52</v>
       </c>
       <c r="T34" t="n">
-        <v>0.17</v>
+        <v>1</v>
       </c>
       <c r="U34" t="n">
-        <v>0.47</v>
+        <v>0.49</v>
       </c>
       <c r="V34" t="n">
-        <v>-0.3</v>
-      </c>
-      <c r="W34" t="n">
-        <v>0.59</v>
-      </c>
+        <v>0.51</v>
+      </c>
+      <c r="W34" t="inlineStr"/>
       <c r="X34" t="n">
         <v>0.48</v>
       </c>
-      <c r="Y34" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>0</v>
-      </c>
+      <c r="Y34" t="inlineStr"/>
+      <c r="Z34" t="inlineStr"/>
       <c r="AA34" t="n">
         <v>0.49</v>
       </c>
-      <c r="AB34" t="n">
-        <v>-0.49</v>
-      </c>
-      <c r="AC34" t="inlineStr"/>
-      <c r="AD34" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="AE34" t="inlineStr"/>
-      <c r="AF34" t="inlineStr"/>
-      <c r="AG34" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="AH34" t="inlineStr"/>
+      <c r="AB34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -4052,7 +3958,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4089,50 +3995,60 @@
           <t>2030-12-31</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr"/>
-      <c r="P35" t="inlineStr"/>
+      <c r="K35" t="n">
+        <v>1</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="N35" t="n">
+        <v>1</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0.05</v>
+      </c>
       <c r="Q35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="S35" t="n">
-        <v>0.05</v>
+        <v>-0.96</v>
       </c>
       <c r="T35" t="n">
         <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="V35" t="n">
-        <v>-0.95</v>
-      </c>
-      <c r="W35" t="inlineStr"/>
+        <v>-0.96</v>
+      </c>
+      <c r="W35" t="n">
+        <v>0</v>
+      </c>
       <c r="X35" t="n">
         <v>0.96</v>
       </c>
-      <c r="Y35" t="inlineStr"/>
-      <c r="Z35" t="inlineStr"/>
+      <c r="Y35" t="n">
+        <v>-0.96</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>0.84</v>
+      </c>
       <c r="AA35" t="n">
         <v>0.96</v>
       </c>
-      <c r="AB35" t="inlineStr"/>
-      <c r="AC35" t="inlineStr"/>
-      <c r="AD35" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="AE35" t="inlineStr"/>
-      <c r="AF35" t="inlineStr"/>
-      <c r="AG35" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="AH35" t="inlineStr"/>
+      <c r="AB35" t="n">
+        <v>-0.12</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -4146,7 +4062,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4183,58 +4099,60 @@
           <t>2030-12-31</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr"/>
-      <c r="P36" t="inlineStr"/>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="M36" t="n">
+        <v>-0.32</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="P36" t="n">
+        <v>-0.16</v>
+      </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>0.18</v>
       </c>
       <c r="R36" t="n">
-        <v>0.32</v>
+        <v>0.35</v>
       </c>
       <c r="S36" t="n">
-        <v>-0.32</v>
+        <v>-0.17</v>
       </c>
       <c r="T36" t="n">
+        <v>0</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="V36" t="n">
+        <v>-0.36</v>
+      </c>
+      <c r="W36" t="n">
         <v>0.18</v>
-      </c>
-      <c r="U36" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="V36" t="n">
-        <v>-0.16</v>
-      </c>
-      <c r="W36" t="n">
-        <v>0</v>
       </c>
       <c r="X36" t="n">
         <v>0.35</v>
       </c>
       <c r="Y36" t="n">
-        <v>-0.35</v>
-      </c>
-      <c r="Z36" t="inlineStr"/>
+        <v>-0.17</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>0</v>
+      </c>
       <c r="AA36" t="n">
         <v>0.36</v>
       </c>
-      <c r="AB36" t="inlineStr"/>
-      <c r="AC36" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="AE36" t="n">
-        <v>-0.17</v>
-      </c>
-      <c r="AF36" t="inlineStr"/>
-      <c r="AG36" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="AH36" t="inlineStr"/>
+      <c r="AB36" t="n">
+        <v>-0.36</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -4248,7 +4166,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4285,62 +4203,60 @@
           <t>2030-12-31</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
-      <c r="O37" t="inlineStr"/>
-      <c r="P37" t="inlineStr"/>
+      <c r="K37" t="n">
+        <v>142</v>
+      </c>
+      <c r="L37" t="n">
+        <v>7.38</v>
+      </c>
+      <c r="M37" t="n">
+        <v>134.62</v>
+      </c>
+      <c r="N37" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="O37" t="n">
+        <v>6.99</v>
+      </c>
+      <c r="P37" t="n">
+        <v>-6.91</v>
+      </c>
       <c r="Q37" t="n">
-        <v>142</v>
+        <v>0.08</v>
       </c>
       <c r="R37" t="n">
-        <v>7.38</v>
+        <v>6.61</v>
       </c>
       <c r="S37" t="n">
-        <v>134.62</v>
+        <v>-6.53</v>
       </c>
       <c r="T37" t="n">
-        <v>0.08</v>
+        <v>10.32</v>
       </c>
       <c r="U37" t="n">
-        <v>6.99</v>
+        <v>6.28</v>
       </c>
       <c r="V37" t="n">
-        <v>-6.91</v>
+        <v>4.04</v>
       </c>
       <c r="W37" t="n">
-        <v>0.08</v>
+        <v>11.1</v>
       </c>
       <c r="X37" t="n">
         <v>6.61</v>
       </c>
       <c r="Y37" t="n">
-        <v>-6.53</v>
+        <v>4.49</v>
       </c>
       <c r="Z37" t="n">
-        <v>10.32</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AA37" t="n">
         <v>6.28</v>
       </c>
       <c r="AB37" t="n">
-        <v>4.04</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>6.61</v>
-      </c>
-      <c r="AE37" t="n">
-        <v>4.49</v>
-      </c>
-      <c r="AF37" t="inlineStr"/>
-      <c r="AG37" t="n">
-        <v>6.28</v>
-      </c>
-      <c r="AH37" t="inlineStr"/>
+        <v>2.92</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/salidas/Base_resultados_PPDJ_python.xlsx
+++ b/salidas/Base_resultados_PPDJ_python.xlsx
@@ -719,55 +719,55 @@
         <v>0.44</v>
       </c>
       <c r="L3" t="n">
-        <v>0.32</v>
+        <v>0.323</v>
       </c>
       <c r="M3" t="n">
-        <v>0.12</v>
+        <v>0.117</v>
       </c>
       <c r="N3" t="n">
         <v>0.44</v>
       </c>
       <c r="O3" t="n">
-        <v>0.33</v>
+        <v>0.333</v>
       </c>
       <c r="P3" t="n">
-        <v>0.11</v>
+        <v>0.107</v>
       </c>
       <c r="Q3" t="n">
         <v>0.34</v>
       </c>
       <c r="R3" t="n">
-        <v>0.34</v>
+        <v>0.343</v>
       </c>
       <c r="S3" t="n">
-        <v>-0</v>
+        <v>-0.003</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>0.35</v>
+        <v>0.353</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.35</v>
+        <v>-0.353</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0.36</v>
+        <v>0.363</v>
       </c>
       <c r="Y3" t="n">
-        <v>-0.36</v>
+        <v>-0.363</v>
       </c>
       <c r="Z3" t="n">
         <v>0.34</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.37</v>
+        <v>0.373</v>
       </c>
       <c r="AB3" t="n">
-        <v>-0.03</v>
+        <v>-0.033</v>
       </c>
     </row>
     <row r="4">
@@ -832,28 +832,28 @@
         <v>0.1</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1</v>
+        <v>0.105</v>
       </c>
       <c r="P4" t="n">
-        <v>-0</v>
+        <v>-0.005</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.1</v>
+        <v>0.105</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.1</v>
+        <v>-0.105</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1</v>
+        <v>0.105</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.1</v>
+        <v>-0.105</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
@@ -933,13 +933,13 @@
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>0.01</v>
+        <v>0.0119</v>
       </c>
       <c r="O5" t="n">
         <v>5</v>
       </c>
       <c r="P5" t="n">
-        <v>-4.99</v>
+        <v>-4.9881</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1027,55 +1027,55 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0.92</v>
+        <v>0.924</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.92</v>
+        <v>-0.924</v>
       </c>
       <c r="N6" t="n">
-        <v>0.01</v>
+        <v>0.0102</v>
       </c>
       <c r="O6" t="n">
-        <v>0.92</v>
+        <v>0.924</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.91</v>
+        <v>-0.9137999999999999</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.11</v>
+        <v>1.106</v>
       </c>
       <c r="R6" t="n">
-        <v>0.92</v>
+        <v>0.924</v>
       </c>
       <c r="S6" t="n">
-        <v>0.18</v>
+        <v>0.182</v>
       </c>
       <c r="T6" t="n">
-        <v>1.04</v>
+        <v>1.0385</v>
       </c>
       <c r="U6" t="n">
-        <v>0.92</v>
+        <v>0.924</v>
       </c>
       <c r="V6" t="n">
-        <v>0.11</v>
+        <v>0.1145</v>
       </c>
       <c r="W6" t="n">
         <v>100.58</v>
       </c>
       <c r="X6" t="n">
-        <v>0.92</v>
+        <v>0.924</v>
       </c>
       <c r="Y6" t="n">
-        <v>99.66</v>
+        <v>99.65600000000001</v>
       </c>
       <c r="Z6" t="n">
         <v>102.02</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.92</v>
+        <v>0.924</v>
       </c>
       <c r="AB6" t="n">
-        <v>101.1</v>
+        <v>101.096</v>
       </c>
     </row>
     <row r="7">
@@ -1131,55 +1131,55 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>0.82</v>
+        <v>0.823</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.82</v>
+        <v>-0.823</v>
       </c>
       <c r="N7" t="n">
-        <v>0.01</v>
+        <v>0.0051</v>
       </c>
       <c r="O7" t="n">
-        <v>0.82</v>
+        <v>0.823</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.82</v>
+        <v>-0.8179</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.98</v>
+        <v>0.978</v>
       </c>
       <c r="R7" t="n">
-        <v>0.82</v>
+        <v>0.823</v>
       </c>
       <c r="S7" t="n">
-        <v>0.16</v>
+        <v>0.155</v>
       </c>
       <c r="T7" t="n">
-        <v>0.99</v>
+        <v>0.9876</v>
       </c>
       <c r="U7" t="n">
-        <v>0.82</v>
+        <v>0.823</v>
       </c>
       <c r="V7" t="n">
-        <v>0.16</v>
+        <v>0.1646</v>
       </c>
       <c r="W7" t="n">
-        <v>0.98</v>
+        <v>0.9754</v>
       </c>
       <c r="X7" t="n">
-        <v>0.82</v>
+        <v>0.823</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.15</v>
+        <v>0.1524</v>
       </c>
       <c r="Z7" t="n">
         <v>101.79</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.82</v>
+        <v>0.823</v>
       </c>
       <c r="AB7" t="n">
-        <v>100.97</v>
+        <v>100.967</v>
       </c>
     </row>
     <row r="8">
@@ -1235,55 +1235,55 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.5580000000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>0.48</v>
+        <v>0.482</v>
       </c>
       <c r="O8" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.08</v>
+        <v>-0.076</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.48</v>
+        <v>0.482</v>
       </c>
       <c r="R8" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.08</v>
+        <v>-0.081</v>
       </c>
       <c r="T8" t="n">
-        <v>0.52</v>
+        <v>0.515</v>
       </c>
       <c r="U8" t="n">
-        <v>0.57</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.05</v>
+        <v>-0.053</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0.57</v>
+        <v>0.573</v>
       </c>
       <c r="Y8" t="n">
-        <v>-0.57</v>
+        <v>-0.573</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.54</v>
+        <v>0.5391</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.58</v>
+        <v>0.578</v>
       </c>
       <c r="AB8" t="n">
-        <v>-0.04</v>
+        <v>-0.0389</v>
       </c>
     </row>
     <row r="9">
@@ -1372,13 +1372,13 @@
         <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1</v>
+        <v>0.9991</v>
       </c>
       <c r="X9" t="n">
         <v>1</v>
       </c>
       <c r="Y9" t="n">
-        <v>-0</v>
+        <v>-0.0009</v>
       </c>
       <c r="Z9" t="n">
         <v>1</v>
@@ -1452,37 +1452,37 @@
         <v>0.35</v>
       </c>
       <c r="O10" t="n">
-        <v>0.32</v>
+        <v>0.3216</v>
       </c>
       <c r="P10" t="n">
-        <v>0.03</v>
+        <v>0.0284</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.35</v>
+        <v>0.352</v>
       </c>
       <c r="R10" t="n">
-        <v>0.32</v>
+        <v>0.3216</v>
       </c>
       <c r="S10" t="n">
-        <v>0.03</v>
+        <v>0.0304</v>
       </c>
       <c r="T10" t="n">
         <v>0.35</v>
       </c>
       <c r="U10" t="n">
-        <v>0.32</v>
+        <v>0.3216</v>
       </c>
       <c r="V10" t="n">
-        <v>0.03</v>
+        <v>0.0284</v>
       </c>
       <c r="W10" t="n">
-        <v>0.33</v>
+        <v>0.325</v>
       </c>
       <c r="X10" t="n">
         <v>0.32</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.01</v>
+        <v>0.005</v>
       </c>
       <c r="Z10" t="n">
         <v>0.33</v>
@@ -1562,31 +1562,31 @@
         <v>-0.13</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.01</v>
+        <v>0.006</v>
       </c>
       <c r="R11" t="n">
         <v>1.53</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.52</v>
+        <v>-1.524</v>
       </c>
       <c r="T11" t="n">
-        <v>0.04</v>
+        <v>0.035</v>
       </c>
       <c r="U11" t="n">
         <v>1.53</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.5</v>
+        <v>-1.495</v>
       </c>
       <c r="W11" t="n">
-        <v>0.02</v>
+        <v>0.0216</v>
       </c>
       <c r="X11" t="n">
         <v>1.53</v>
       </c>
       <c r="Y11" t="n">
-        <v>-1.51</v>
+        <v>-1.5084</v>
       </c>
       <c r="Z11" t="n">
         <v>2</v>
@@ -1673,13 +1673,13 @@
       <c r="X12" t="inlineStr"/>
       <c r="Y12" t="inlineStr"/>
       <c r="Z12" t="n">
-        <v>0.09</v>
+        <v>0.0949</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.09</v>
+        <v>0.0906</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>0.0043</v>
       </c>
     </row>
     <row r="13">
@@ -1741,31 +1741,31 @@
         <v>0.37</v>
       </c>
       <c r="N13" t="n">
-        <v>0.25</v>
+        <v>0.251</v>
       </c>
       <c r="O13" t="n">
         <v>0.27</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.02</v>
+        <v>-0.019</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.91</v>
+        <v>0.9079</v>
       </c>
       <c r="R13" t="n">
         <v>0.28</v>
       </c>
       <c r="S13" t="n">
-        <v>0.63</v>
+        <v>0.6279</v>
       </c>
       <c r="T13" t="n">
-        <v>0.31</v>
+        <v>0.3085</v>
       </c>
       <c r="U13" t="n">
         <v>0.3</v>
       </c>
       <c r="V13" t="n">
-        <v>0.01</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="W13" t="n">
         <v>0.5</v>
@@ -1863,22 +1863,22 @@
         <v>-0.27</v>
       </c>
       <c r="T14" t="n">
-        <v>0.11</v>
+        <v>0.1053</v>
       </c>
       <c r="U14" t="n">
         <v>0.4</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.29</v>
+        <v>-0.2947</v>
       </c>
       <c r="W14" t="n">
-        <v>0.17</v>
+        <v>0.172</v>
       </c>
       <c r="X14" t="n">
         <v>0.4</v>
       </c>
       <c r="Y14" t="n">
-        <v>-0.23</v>
+        <v>-0.228</v>
       </c>
       <c r="Z14" t="n">
         <v>0.16</v>
@@ -1940,58 +1940,58 @@
         </is>
       </c>
       <c r="K15" t="n">
-        <v>0.28</v>
+        <v>0.2771</v>
       </c>
       <c r="L15" t="n">
-        <v>0.23</v>
+        <v>0.233</v>
       </c>
       <c r="M15" t="n">
-        <v>0.04</v>
+        <v>0.0441</v>
       </c>
       <c r="N15" t="n">
         <v>4.94</v>
       </c>
       <c r="O15" t="n">
-        <v>0.25</v>
+        <v>0.252</v>
       </c>
       <c r="P15" t="n">
-        <v>4.69</v>
+        <v>4.688</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.36</v>
+        <v>0.3625</v>
       </c>
       <c r="R15" t="n">
-        <v>0.27</v>
+        <v>0.2663</v>
       </c>
       <c r="S15" t="n">
-        <v>0.1</v>
+        <v>0.09619999999999999</v>
       </c>
       <c r="T15" t="n">
-        <v>0.36</v>
+        <v>0.3626</v>
       </c>
       <c r="U15" t="n">
-        <v>0.28</v>
+        <v>0.2762</v>
       </c>
       <c r="V15" t="n">
-        <v>0.09</v>
+        <v>0.0864</v>
       </c>
       <c r="W15" t="n">
-        <v>0.36</v>
+        <v>0.3626</v>
       </c>
       <c r="X15" t="n">
-        <v>0.29</v>
+        <v>0.2885</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.0741</v>
       </c>
       <c r="Z15" t="n">
-        <v>0.36</v>
+        <v>0.3626</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.3</v>
+        <v>0.3008</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.06</v>
+        <v>0.0618</v>
       </c>
     </row>
     <row r="16">
@@ -2261,22 +2261,22 @@
         <v>27.16</v>
       </c>
       <c r="N18" t="n">
-        <v>0.3</v>
+        <v>0.3005</v>
       </c>
       <c r="O18" t="n">
         <v>34.6</v>
       </c>
       <c r="P18" t="n">
-        <v>-34.3</v>
+        <v>-34.2995</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.22</v>
+        <v>0.2195</v>
       </c>
       <c r="R18" t="n">
         <v>32.8</v>
       </c>
       <c r="S18" t="n">
-        <v>-32.58</v>
+        <v>-32.5805</v>
       </c>
       <c r="T18" t="n">
         <v>41.4</v>
@@ -2472,46 +2472,46 @@
         <v>0.2</v>
       </c>
       <c r="O20" t="n">
-        <v>0.1</v>
+        <v>0.104</v>
       </c>
       <c r="P20" t="n">
-        <v>0.1</v>
+        <v>0.096</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.11</v>
+        <v>0.114</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.11</v>
+        <v>-0.114</v>
       </c>
       <c r="T20" t="n">
-        <v>0.03</v>
+        <v>0.033</v>
       </c>
       <c r="U20" t="n">
-        <v>0.12</v>
+        <v>0.124</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.09</v>
+        <v>-0.091</v>
       </c>
       <c r="W20" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.0675</v>
       </c>
       <c r="X20" t="n">
-        <v>0.12</v>
+        <v>0.124</v>
       </c>
       <c r="Y20" t="n">
-        <v>-0.06</v>
+        <v>-0.0565</v>
       </c>
       <c r="Z20" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.0675</v>
       </c>
       <c r="AA20" t="n">
-        <v>0.13</v>
+        <v>0.134</v>
       </c>
       <c r="AB20" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.0665</v>
       </c>
     </row>
     <row r="21">
@@ -2567,55 +2567,55 @@
         <v>0.18</v>
       </c>
       <c r="L21" t="n">
-        <v>0.32</v>
+        <v>0.323</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.14</v>
+        <v>-0.143</v>
       </c>
       <c r="N21" t="n">
         <v>0.18</v>
       </c>
       <c r="O21" t="n">
-        <v>0.34</v>
+        <v>0.343</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.16</v>
+        <v>-0.163</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.36</v>
+        <v>0.363</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.36</v>
+        <v>-0.363</v>
       </c>
       <c r="T21" t="n">
-        <v>0.14</v>
+        <v>0.144</v>
       </c>
       <c r="U21" t="n">
-        <v>0.38</v>
+        <v>0.383</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.24</v>
+        <v>-0.239</v>
       </c>
       <c r="W21" t="n">
-        <v>0.14</v>
+        <v>0.1353</v>
       </c>
       <c r="X21" t="n">
-        <v>0.38</v>
+        <v>0.383</v>
       </c>
       <c r="Y21" t="n">
-        <v>-0.25</v>
+        <v>-0.2477</v>
       </c>
       <c r="Z21" t="n">
-        <v>0.14</v>
+        <v>0.1353</v>
       </c>
       <c r="AA21" t="n">
-        <v>0.4</v>
+        <v>0.403</v>
       </c>
       <c r="AB21" t="n">
-        <v>-0.27</v>
+        <v>-0.2677</v>
       </c>
     </row>
     <row r="22">
@@ -2686,13 +2686,13 @@
         <v>-3.8</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.068</v>
       </c>
       <c r="R22" t="n">
         <v>5</v>
       </c>
       <c r="S22" t="n">
-        <v>-4.93</v>
+        <v>-4.932</v>
       </c>
       <c r="T22" t="n">
         <v>6.03</v>
@@ -2808,13 +2808,13 @@
         <v>-0.11</v>
       </c>
       <c r="W23" t="n">
-        <v>0.52</v>
+        <v>0.5165</v>
       </c>
       <c r="X23" t="n">
         <v>0.61</v>
       </c>
       <c r="Y23" t="n">
-        <v>-0.09</v>
+        <v>-0.0935</v>
       </c>
       <c r="Z23" t="n">
         <v>0.52</v>
@@ -3092,28 +3092,28 @@
         <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>1062.26</v>
+        <v>1062.2569</v>
       </c>
       <c r="P26" t="n">
-        <v>-1062.26</v>
+        <v>-1062.2569</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>1045.83</v>
+        <v>1045.8303</v>
       </c>
       <c r="S26" t="n">
-        <v>-1045.83</v>
+        <v>-1045.8303</v>
       </c>
       <c r="T26" t="n">
         <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>1029.4</v>
+        <v>1029.4036</v>
       </c>
       <c r="V26" t="n">
-        <v>-1029.4</v>
+        <v>-1029.4036</v>
       </c>
       <c r="W26" t="n">
         <v>0</v>
@@ -3287,55 +3287,55 @@
         <v>0.4</v>
       </c>
       <c r="L28" t="n">
-        <v>1</v>
+        <v>0.9999</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.6</v>
+        <v>-0.5999</v>
       </c>
       <c r="N28" t="n">
         <v>0.51</v>
       </c>
       <c r="O28" t="n">
-        <v>1</v>
+        <v>0.9998</v>
       </c>
       <c r="P28" t="n">
-        <v>-0.49</v>
+        <v>-0.4898</v>
       </c>
       <c r="Q28" t="n">
         <v>1.1</v>
       </c>
       <c r="R28" t="n">
-        <v>1</v>
+        <v>0.9997</v>
       </c>
       <c r="S28" t="n">
-        <v>0.1</v>
+        <v>0.1003</v>
       </c>
       <c r="T28" t="n">
         <v>1.62</v>
       </c>
       <c r="U28" t="n">
-        <v>1</v>
+        <v>0.9996</v>
       </c>
       <c r="V28" t="n">
-        <v>0.62</v>
+        <v>0.6204</v>
       </c>
       <c r="W28" t="n">
         <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>1</v>
+        <v>0.9995000000000001</v>
       </c>
       <c r="Y28" t="n">
-        <v>-1</v>
+        <v>-0.9995000000000001</v>
       </c>
       <c r="Z28" t="n">
-        <v>3.06</v>
+        <v>3.0612</v>
       </c>
       <c r="AA28" t="n">
-        <v>1</v>
+        <v>0.9994</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.06</v>
+        <v>2.0618</v>
       </c>
     </row>
     <row r="29">
@@ -3391,55 +3391,55 @@
         <v>0.4</v>
       </c>
       <c r="L29" t="n">
-        <v>0.01</v>
+        <v>0.0109</v>
       </c>
       <c r="M29" t="n">
-        <v>0.39</v>
+        <v>0.3891</v>
       </c>
       <c r="N29" t="n">
         <v>0.82</v>
       </c>
       <c r="O29" t="n">
-        <v>0.01</v>
+        <v>0.0109</v>
       </c>
       <c r="P29" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.8091</v>
       </c>
       <c r="Q29" t="n">
         <v>3.04</v>
       </c>
       <c r="R29" t="n">
-        <v>0.01</v>
+        <v>0.0108</v>
       </c>
       <c r="S29" t="n">
-        <v>3.03</v>
+        <v>3.0292</v>
       </c>
       <c r="T29" t="n">
         <v>3.83</v>
       </c>
       <c r="U29" t="n">
-        <v>0.01</v>
+        <v>0.0107</v>
       </c>
       <c r="V29" t="n">
-        <v>3.82</v>
+        <v>3.8193</v>
       </c>
       <c r="W29" t="n">
         <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>0.01</v>
+        <v>0.0107</v>
       </c>
       <c r="Y29" t="n">
-        <v>-0.01</v>
+        <v>-0.0107</v>
       </c>
       <c r="Z29" t="n">
         <v>4.66</v>
       </c>
       <c r="AA29" t="n">
-        <v>0.01</v>
+        <v>0.0106</v>
       </c>
       <c r="AB29" t="n">
-        <v>4.65</v>
+        <v>4.6494</v>
       </c>
     </row>
     <row r="30">
@@ -3495,50 +3495,50 @@
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>0.89</v>
+        <v>0.8863</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.89</v>
+        <v>-0.8863</v>
       </c>
       <c r="N30" t="n">
         <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>0.88</v>
+        <v>0.8763</v>
       </c>
       <c r="P30" t="n">
-        <v>-0.88</v>
+        <v>-0.8763</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>0.87</v>
+        <v>0.8663</v>
       </c>
       <c r="S30" t="n">
-        <v>-0.87</v>
+        <v>-0.8663</v>
       </c>
       <c r="T30" t="n">
         <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>0.86</v>
+        <v>0.8563</v>
       </c>
       <c r="V30" t="n">
-        <v>-0.86</v>
+        <v>-0.8563</v>
       </c>
       <c r="W30" t="n">
         <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>0.86</v>
+        <v>0.8563</v>
       </c>
       <c r="Y30" t="n">
-        <v>-0.86</v>
+        <v>-0.8563</v>
       </c>
       <c r="Z30" t="inlineStr"/>
       <c r="AA30" t="n">
-        <v>0.85</v>
+        <v>0.8463000000000001</v>
       </c>
       <c r="AB30" t="inlineStr"/>
     </row>
@@ -3699,50 +3699,50 @@
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>0.19</v>
+        <v>0.1919</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.19</v>
+        <v>-0.1919</v>
       </c>
       <c r="N32" t="n">
         <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>0.19</v>
+        <v>0.1908</v>
       </c>
       <c r="P32" t="n">
-        <v>-0.19</v>
+        <v>-0.1908</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>0.19</v>
+        <v>0.1897</v>
       </c>
       <c r="S32" t="n">
-        <v>-0.19</v>
+        <v>-0.1897</v>
       </c>
       <c r="T32" t="n">
         <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>0.19</v>
+        <v>0.1886</v>
       </c>
       <c r="V32" t="n">
-        <v>-0.19</v>
+        <v>-0.1886</v>
       </c>
       <c r="W32" t="n">
         <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>0.19</v>
+        <v>0.1886</v>
       </c>
       <c r="Y32" t="n">
-        <v>-0.19</v>
+        <v>-0.1886</v>
       </c>
       <c r="Z32" t="inlineStr"/>
       <c r="AA32" t="n">
-        <v>0.19</v>
+        <v>0.1875</v>
       </c>
       <c r="AB32" t="inlineStr"/>
     </row>
@@ -3796,58 +3796,58 @@
         </is>
       </c>
       <c r="K33" t="n">
-        <v>0.1</v>
+        <v>0.1005</v>
       </c>
       <c r="L33" t="n">
-        <v>0.61</v>
+        <v>0.613</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.51</v>
+        <v>-0.5125</v>
       </c>
       <c r="N33" t="n">
         <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>0.61</v>
+        <v>0.6145</v>
       </c>
       <c r="P33" t="n">
-        <v>-0.61</v>
+        <v>-0.6145</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.25</v>
+        <v>0.2525</v>
       </c>
       <c r="R33" t="n">
-        <v>0.62</v>
+        <v>0.616</v>
       </c>
       <c r="S33" t="n">
-        <v>-0.36</v>
+        <v>-0.3635</v>
       </c>
       <c r="T33" t="n">
         <v>0.98</v>
       </c>
       <c r="U33" t="n">
-        <v>0.62</v>
+        <v>0.6175</v>
       </c>
       <c r="V33" t="n">
-        <v>0.36</v>
+        <v>0.3625</v>
       </c>
       <c r="W33" t="n">
         <v>0.99</v>
       </c>
       <c r="X33" t="n">
-        <v>0.62</v>
+        <v>0.6175</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.37</v>
+        <v>0.3725</v>
       </c>
       <c r="Z33" t="n">
         <v>0.99</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.62</v>
+        <v>0.619</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.37</v>
+        <v>0.371</v>
       </c>
     </row>
     <row r="34">
@@ -3900,22 +3900,22 @@
         </is>
       </c>
       <c r="K34" t="n">
-        <v>0.24</v>
+        <v>0.2354</v>
       </c>
       <c r="L34" t="n">
         <v>0.45</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.21</v>
+        <v>-0.2146</v>
       </c>
       <c r="N34" t="n">
-        <v>0.41</v>
+        <v>0.4079</v>
       </c>
       <c r="O34" t="n">
         <v>0.47</v>
       </c>
       <c r="P34" t="n">
-        <v>-0.06</v>
+        <v>-0.0621</v>
       </c>
       <c r="Q34" t="n">
         <v>1</v>
@@ -3999,28 +3999,28 @@
         <v>1</v>
       </c>
       <c r="L35" t="n">
-        <v>0.95</v>
+        <v>0.951</v>
       </c>
       <c r="M35" t="n">
-        <v>0.05</v>
+        <v>0.049</v>
       </c>
       <c r="N35" t="n">
         <v>1</v>
       </c>
       <c r="O35" t="n">
-        <v>0.95</v>
+        <v>0.954</v>
       </c>
       <c r="P35" t="n">
-        <v>0.05</v>
+        <v>0.046</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>0.96</v>
+        <v>0.957</v>
       </c>
       <c r="S35" t="n">
-        <v>-0.96</v>
+        <v>-0.957</v>
       </c>
       <c r="T35" t="n">
         <v>0</v>
@@ -4035,10 +4035,10 @@
         <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>0.96</v>
+        <v>0.957</v>
       </c>
       <c r="Y35" t="n">
-        <v>-0.96</v>
+        <v>-0.957</v>
       </c>
       <c r="Z35" t="n">
         <v>0.84</v>
@@ -4112,10 +4112,10 @@
         <v>0.18</v>
       </c>
       <c r="O36" t="n">
-        <v>0.34</v>
+        <v>0.335</v>
       </c>
       <c r="P36" t="n">
-        <v>-0.16</v>
+        <v>-0.155</v>
       </c>
       <c r="Q36" t="n">
         <v>0.18</v>
@@ -4130,10 +4130,10 @@
         <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>0.36</v>
+        <v>0.365</v>
       </c>
       <c r="V36" t="n">
-        <v>-0.36</v>
+        <v>-0.365</v>
       </c>
       <c r="W36" t="n">
         <v>0.18</v>
@@ -4148,10 +4148,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>0.36</v>
+        <v>0.365</v>
       </c>
       <c r="AB36" t="n">
-        <v>-0.36</v>
+        <v>-0.365</v>
       </c>
     </row>
     <row r="37">
@@ -4213,31 +4213,31 @@
         <v>134.62</v>
       </c>
       <c r="N37" t="n">
-        <v>0.08</v>
+        <v>0.0827</v>
       </c>
       <c r="O37" t="n">
-        <v>6.99</v>
+        <v>6.9925</v>
       </c>
       <c r="P37" t="n">
-        <v>-6.91</v>
+        <v>-6.9098</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.08</v>
+        <v>0.0827</v>
       </c>
       <c r="R37" t="n">
-        <v>6.61</v>
+        <v>6.6123</v>
       </c>
       <c r="S37" t="n">
-        <v>-6.53</v>
+        <v>-6.5296</v>
       </c>
       <c r="T37" t="n">
         <v>10.32</v>
       </c>
       <c r="U37" t="n">
-        <v>6.28</v>
+        <v>6.2823</v>
       </c>
       <c r="V37" t="n">
-        <v>4.04</v>
+        <v>4.0377</v>
       </c>
       <c r="W37" t="n">
         <v>11.1</v>
